--- a/artfynd/A 36456-2021 artfynd.xlsx
+++ b/artfynd/A 36456-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36456-2021 artfynd.xlsx
+++ b/artfynd/A 36456-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1874610</v>
+        <v>902606</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kotjärnbäcken, Jmt</t>
+          <t>Märlingsbergets mångfaldspark, Bräcke, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512474.6208138745</v>
+        <v>512384</v>
       </c>
       <c r="R2" t="n">
-        <v>6952690.406883223</v>
+        <v>6952929</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-10-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,16 +756,29 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gallrad barrskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter # gamla sälgar</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1981474</v>
+        <v>1874610</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512538.5911815159</v>
+        <v>512475</v>
       </c>
       <c r="R3" t="n">
-        <v>6952789.325731466</v>
+        <v>6952690</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +857,9 @@
           <t>2012-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +887,623 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1981469</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>512446</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6952752</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1981474</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512539</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6952789</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-10-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-10-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000501</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>512476</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6952947</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2000502</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>512387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6952922</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2073380</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kotjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>512420</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6952866</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-10-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15371166</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Märlingsbergets mångfaldspark, Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>512501</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6952931</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Typiska spår i 1 träd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>grov tallöverståndare, mager barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
